--- a/b2b.xlsx
+++ b/b2b.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,6 +443,486 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>b2b</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>/market/?f_keyword=%D1%82%D1%80%D1%83%D0%B1%D1%8B&amp;searching=1&amp;trade=all&amp;order_by=1&amp;order_by_prev=0&amp;order_dir_prev=0</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>b2b</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Трубычерные бесшовные - ООО "СУЭК-Хакасия" - Хакасия</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>/app/market-next/truby-chernye-besshovnye-ooo-suek-khakasiia-khakasiia/tender-4588768/#btid=2&amp;sqh=b3131438206d139f71d873f3251621eb8aa2ced8&amp;tsid=4588768458</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>04.09.2026 08:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>b2b</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Закупкатрубстальных для АО "Быстринская горная компания"Трубыстальные</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>/market/zakupka-trub-stalnykh-dlia-ao-bystrinskaia-gornaia-kompaniia/tender-4589292/#btid=2&amp;sqh=b3131438206d139f71d873f3251621eb8aa2ced8&amp;tsid=4589292004</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>04.09.2026 11:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>b2b</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ТрубыСт20 (2080001-001)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>/app/market-next/truby-st20-2080001-001/tender-4589580/#btid=2&amp;sqh=b3131438206d139f71d873f3251621eb8aa2ced8&amp;tsid=4589580462</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>04.09.2026 14:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>b2b</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Поставкатруббесшовный АО "Алтай-кокс" г. Заринск</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>/app/market-next/postavka-trub-besshovnyi-ao-altai-koks-g-zarinsk/tender-4589673/#btid=2&amp;sqh=b3131438206d139f71d873f3251621eb8aa2ced8&amp;tsid=4589673462</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>04.09.2026 13:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>b2b</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Поставкатрубстальных бесшовных АО "СГОК" г. Старый Оскол</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>/app/market-next/postavka-trub-stalnykh-besshovnykh-ao-sgok-g-staryi-oskol/tender-4589260/#btid=2&amp;sqh=b3131438206d139f71d873f3251621eb8aa2ced8&amp;tsid=4589260462</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>04.09.2026 11:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>b2b</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Труба89х10 ГОСТ 8731-74/ ГОСТ 8732-78</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>/market/truba-89kh10/tender-4589980/#btid=2&amp;sqh=b3131438206d139f71d873f3251621eb8aa2ced8&amp;tsid=4589980004</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>04.09.2026 15:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>b2b</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Поставкатрубэлектросварных для АО "Алтай-кокс" г. Заринск</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>/app/market-next/postavka-trub-elektrosvarnykh-dlia-ao-altai-koks-g-zarinsk/tender-4589880/#btid=2&amp;sqh=b3131438206d139f71d873f3251621eb8aa2ced8&amp;tsid=4589880462</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>04.09.2026 14:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>b2b</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Поставка стальныхтруб</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>/app/market-next/postavka-stalnykh-trub/tender-4589575/#btid=2&amp;sqh=b3131438206d139f71d873f3251621eb8aa2ced8&amp;tsid=4589575459</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>04.09.2026 13:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>b2b</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Продажатрубынержавеющей 20х1,5 б/у на ПАО "Уралкуз" См. подгруженное фото</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>/market/prodazha-truby-nerzhaveiushchei-20kh1-5-b-u-na-pao-uralkuz/tender-4587999/#btid=2&amp;sqh=b3131438206d139f71d873f3251621eb8aa2ced8&amp;tsid=4587999003</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>04.09.2026 08:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>b2b</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>БЕЗ ПЕРЕТОРЖКИ!!! Отводы, задвижки,трубыдля АО Кудряшовское. Срок поставки на склад согласно извещению до 10.09.2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>/market/bez-peretorzhki-otvody-zadvizhki-truby-dlia-ao-kudriashovskoe-srok/tender-4589230/#btid=2&amp;sqh=b3131438206d139f71d873f3251621eb8aa2ced8&amp;tsid=4589230004</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>04.09.2026 11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>b2b</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Трубаэлектропроводящая, Провод для взрывных работ (Средства инициирования для ОЗРК). Процедура проводится в 1 этап (без переторжек). Самовывоз. В стоимость товара включить стоимость Северной упаковки, обрешетки. 2 конечных получателя. ОБЯЗАТЕЛЬНО заполнение полной информации в таблице. Процедура проводится в 1 этап (без переторжек). Самовывоз. В стоимость товара включить стоимость Северной упаковки, обрешетки. 2 конечных получателя. ОБЯЗАТЕЛЬНО заполнение полной информации в таблице.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>/market/truba-elektroprovodiashchaia-provod-dlia-vzryvnykh-rabot-sredstva/tender-4588575/#btid=2&amp;sqh=b3131438206d139f71d873f3251621eb8aa2ced8&amp;tsid=4588575004</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>04.09.2026 04:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>b2b</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ПродажаТРУБАГ/К СТ20 168Х25,ТРУБАБЕСШ. Г/Д СТ20 426Х9-10 на Челябинском филиале ПАО "Уралкуз"</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>/market/prodazha-truba-g-k-st20-168kh25-truba-bessh-g-d-st20-426kh9-10-na/tender-4588667/#btid=2&amp;sqh=b3131438206d139f71d873f3251621eb8aa2ced8&amp;tsid=4588667003</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>04.09.2026 08:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>b2b</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Поставкатрубстальных в ППУ изоляции и комплектующих к ним Лот № 1. Поставкатрубстальных в ППУ изоляции и комплектующих к ним</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>/market/postavka-trub-stalnykh-v-ppu-izoliatsii-i-komplektuiushchikh-k-nim/tenders-57457/#btid=2&amp;sqh=b3131438206d139f71d873f3251621eb8aa2ced8&amp;tsid=57457055</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>04.09.2026 10:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>b2b</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Выбор Поставщика «ТрубаПЭ 100 и скорлупа» для ООО «ГРК «Быстринское»</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>/market/vybor-postavshchika-truba-pe-100-i-skorlupa-dlia-ooo-grk-bystrinskoe/tender-4589273/#btid=2&amp;sqh=b3131438206d139f71d873f3251621eb8aa2ced8&amp;tsid=4589273004</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>04.09.2026 11:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>b2b</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Дождевая канализация для объектов: "Многоэтажные жилые дома и сооружения для инженерного обеспечения объектов по ул. Нижне-Луговой, 18 в г. Томске."... 21.21-031-73011750-2021Трубыиз полиэтилена РЕ Корсис номинальным ... 21.21-031-73011750-2021Трубыиз полиэтилена РЕ Корсис  ... футляр) ГОСТ 9.602-2016Трубастальная электросварная d530х9,0 в  ... ГОСТ 33259-2015 Патрубок изтрубстальных электросварных d426х8 L=0 ...</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>/app/market-next/dozhdevaia-kanalizatsiia-dlia-ob-ektov-mnogoetazhnye-zhilye-doma-i/tender-4588602/#btid=2&amp;sqh=b3131438206d139f71d873f3251621eb8aa2ced8&amp;tsid=4588602458</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>04.09.2026 06:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>b2b</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Канализационная насосная станция дождевых сточных вод  -К2- (37-24 ЛКНС) для объектов: "Многоэтажные жилые дома и сооружения для инженерного обеспечения объектов по ул. Нижне-Луговой, 18 в г. Томске."...  обратный клапан Dn50 Фланцевый выход напорнойтрубыDn50 Ремень крепёжный (РСm, 5.0 ...  из нерж.стали для корзины Вентиляционнаятрубас колпак-дефлектором Кабель-канал для ...</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>/app/market-next/kanalizatsionnaia-nasosnaia-stantsiia-dozhdevykh-stochnykh-vod-k2-37-24/tender-4588662/#btid=2&amp;sqh=b3131438206d139f71d873f3251621eb8aa2ced8&amp;tsid=4588662458</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>04.09.2026 06:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>b2b</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Поставка распылительных форсунок и креплений к ним.... /4". (должны подходить под внешний dтрубы26,9 мм)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>/app/market-next/postavka-raspylitelnykh-forsunok-i-kreplenii-k-nim/tender-4589037/#btid=2&amp;sqh=b3131438206d139f71d873f3251621eb8aa2ced8&amp;tsid=4589037458</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>04.09.2026 10:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>b2b</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Поставка вал карданный к фронтальному погрузчику Hyundai HL 760-9S.  Для ООО "Сибантрацит Майнинг" (по потребности СММО-001982)
+Патрубок, 11LQ-40050, для фронтального погрузчика Hyundai,Трубка гидросистемы, 31LQ-20740-01 фронтальный погрузчик HyundaiТруба, 31LQ-20740 Патрубок, 11LQ-40050, для фронтального погрузчика Hyundai</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>/market/postavka-val-kardannyi-k-frontalnomu-pogruzchiku-hyundai-hl-760-9s/tender-4588603/#btid=2&amp;sqh=b3131438206d139f71d873f3251621eb8aa2ced8&amp;tsid=4588603004</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>04.09.2026 04:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>b2b</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>электротехническая продукция
+Жесткая упаковка для районов крайнего Севера!
+Обязательно прикреплять КП в формате Excel.
+электротехническая продукция
+Жесткая упаковка для районов крайнего Севера!
+Обязательно прикреплять КП в формате Excel.Трубагофрированная строительная ПНД, 63мм, безгалогенная с  ...</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>/market/elektrotekhnicheskaia-produktsiia-zhestkaia-upakovka-dlia-raionov-krainego/tender-4588988/#btid=2&amp;sqh=b3131438206d139f71d873f3251621eb8aa2ced8&amp;tsid=4588988004</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>04.09.2026 09:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>b2b</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Металлопрокат, детали трубопровода сталь: SUSF316 европейского производства_ПМУ_март 2026ТрубаФ139,8х22 Отвод Ф139,8х22 Тройник  ...</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>/app/market-next/metalloprokat-detali-truboprovoda-stal-susf316-evropeiskogo/tender-4589197/#btid=2&amp;sqh=b3131438206d139f71d873f3251621eb8aa2ced8&amp;tsid=4589197462</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>04.09.2026 14:27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
